--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/OKLAHOMA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/OKLAHOMA_2023.xlsx
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C169">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C201">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C304">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C313">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C417">
